--- a/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
@@ -40,6 +40,9 @@
     <x:t>Errores</x:t>
   </x:si>
   <x:si>
+    <x:t>Codigo Objeto</x:t>
+  </x:si>
+  <x:si>
     <x:t>0000</x:t>
   </x:si>
   <x:si>
@@ -73,6 +76,9 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
+    <x:t>040000</x:t>
+  </x:si>
+  <x:si>
     <x:t>0003</x:t>
   </x:si>
   <x:si>
@@ -82,6 +88,9 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
+    <x:t>Error: Mnemónico no reconocido</x:t>
+  </x:si>
+  <x:si>
     <x:t>0004</x:t>
   </x:si>
   <x:si>
@@ -94,6 +103,9 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
+    <x:t>68000000</x:t>
+  </x:si>
+  <x:si>
     <x:t>0008</x:t>
   </x:si>
   <x:si>
@@ -106,6 +118,9 @@
     <x:t>Indirecto</x:t>
   </x:si>
   <x:si>
+    <x:t>0C0000</x:t>
+  </x:si>
+  <x:si>
     <x:t>000B</x:t>
   </x:si>
   <x:si>
@@ -121,6 +136,9 @@
     <x:t>--</x:t>
   </x:si>
   <x:si>
+    <x:t>F2_OBJ</x:t>
+  </x:si>
+  <x:si>
     <x:t>000D</x:t>
   </x:si>
   <x:si>
@@ -151,6 +169,9 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
+    <x:t>180000</x:t>
+  </x:si>
+  <x:si>
     <x:t>0012</x:t>
   </x:si>
   <x:si>
@@ -163,12 +184,21 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
+    <x:t>Error: Símbolo no encontrado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0C000000</x:t>
+  </x:si>
+  <x:si>
     <x:t>0016</x:t>
   </x:si>
   <x:si>
     <x:t>RSUB</x:t>
   </x:si>
   <x:si>
+    <x:t>4C0000</x:t>
+  </x:si>
+  <x:si>
     <x:t>0019</x:t>
   </x:si>
   <x:si>
@@ -211,6 +241,9 @@
     <x:t>C'TEST'</x:t>
   </x:si>
   <x:si>
+    <x:t>54455354</x:t>
+  </x:si>
+  <x:si>
     <x:t>004F</x:t>
   </x:si>
   <x:si>
@@ -218,6 +251,9 @@
   </x:si>
   <x:si>
     <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000010</x:t>
   </x:si>
   <x:si>
     <x:t>0052</x:t>
@@ -574,10 +610,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:H18"/>
+  <x:dimension ref="A1:I18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -602,447 +638,501 @@
       <x:c r="H1" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8">
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H8" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="E9" s="0" t="s">
+      <x:c r="G9" s="0" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>40</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
+      <x:c r="A16" s="0">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D16" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E16" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="F16" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="H15" s="0" t="s">
+      <x:c r="G16" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" spans="1:8">
-      <x:c r="A16" s="0">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D16" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E16" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F16" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="F17" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="F17" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:8">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D18" s="0" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E18" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F18" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D18" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E18" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
@@ -64,6 +64,9 @@
     <x:t/>
   </x:si>
   <x:si>
+    <x:t>----</x:t>
+  </x:si>
+  <x:si>
     <x:t>LDX</x:t>
   </x:si>
   <x:si>
@@ -76,7 +79,7 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
-    <x:t>040000</x:t>
+    <x:t>***F3***</x:t>
   </x:si>
   <x:si>
     <x:t>0003</x:t>
@@ -88,7 +91,7 @@
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Mnemónico no reconocido</x:t>
+    <x:t>F4</x:t>
   </x:si>
   <x:si>
     <x:t>0004</x:t>
@@ -103,7 +106,7 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>68000000</x:t>
+    <x:t>***F4***</x:t>
   </x:si>
   <x:si>
     <x:t>0008</x:t>
@@ -118,9 +121,6 @@
     <x:t>Indirecto</x:t>
   </x:si>
   <x:si>
-    <x:t>0C0000</x:t>
-  </x:si>
-  <x:si>
     <x:t>000B</x:t>
   </x:si>
   <x:si>
@@ -136,7 +136,7 @@
     <x:t>--</x:t>
   </x:si>
   <x:si>
-    <x:t>F2_OBJ</x:t>
+    <x:t>B400</x:t>
   </x:si>
   <x:si>
     <x:t>000D</x:t>
@@ -154,6 +154,9 @@
     <x:t>X,A</x:t>
   </x:si>
   <x:si>
+    <x:t>9010</x:t>
+  </x:si>
+  <x:si>
     <x:t>000F</x:t>
   </x:si>
   <x:si>
@@ -169,9 +172,6 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
-    <x:t>180000</x:t>
-  </x:si>
-  <x:si>
     <x:t>0012</x:t>
   </x:si>
   <x:si>
@@ -184,21 +184,12 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Símbolo no encontrado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0C000000</x:t>
-  </x:si>
-  <x:si>
     <x:t>0016</x:t>
   </x:si>
   <x:si>
     <x:t>RSUB</x:t>
   </x:si>
   <x:si>
-    <x:t>4C0000</x:t>
-  </x:si>
-  <x:si>
     <x:t>0019</x:t>
   </x:si>
   <x:si>
@@ -218,6 +209,9 @@
   </x:si>
   <x:si>
     <x:t>X,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Error: Registro inválido en segundo operando</x:t>
   </x:si>
   <x:si>
     <x:t>002D</x:t>
@@ -668,7 +662,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
@@ -682,22 +676,22 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:9">
@@ -705,28 +699,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:9">
@@ -734,28 +728,28 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:9">
@@ -763,28 +757,28 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -842,7 +836,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:9">
@@ -871,7 +865,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -879,28 +873,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -920,16 +914,16 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -937,19 +931,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>15</x:v>
@@ -958,7 +952,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -966,16 +960,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
         <x:v>61</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>13</x:v>
@@ -987,7 +981,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I13" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:9">
@@ -995,16 +989,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
         <x:v>38</x:v>
@@ -1013,10 +1007,10 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:9">
@@ -1024,16 +1018,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C15" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D15" s="0" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C15" s="0" t="s">
+      <x:c r="E15" s="0" t="s">
         <x:v>69</x:v>
-      </x:c>
-      <x:c r="D15" s="0" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E15" s="0" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>13</x:v>
@@ -1045,7 +1039,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:9">
@@ -1053,16 +1047,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>13</x:v>
@@ -1074,7 +1068,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1082,16 +1076,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C17" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D17" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E17" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="C17" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D17" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="E17" s="0" t="s">
-        <x:v>78</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>13</x:v>
@@ -1103,7 +1097,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1111,13 +1105,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>15</x:v>
@@ -1132,7 +1126,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/ejer1_ArchivoIntermedio.xlsx
@@ -79,7 +79,7 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
-    <x:t>***F3***</x:t>
+    <x:t>050005</x:t>
   </x:si>
   <x:si>
     <x:t>0003</x:t>
@@ -106,7 +106,7 @@
     <x:t>4</x:t>
   </x:si>
   <x:si>
-    <x:t>***F4***</x:t>
+    <x:t>6910004B*</x:t>
   </x:si>
   <x:si>
     <x:t>0008</x:t>
@@ -121,6 +121,9 @@
     <x:t>Indirecto</x:t>
   </x:si>
   <x:si>
+    <x:t>0E200E</x:t>
+  </x:si>
+  <x:si>
     <x:t>000B</x:t>
   </x:si>
   <x:si>
@@ -172,6 +175,9 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
+    <x:t>1BA01B</x:t>
+  </x:si>
+  <x:si>
     <x:t>0012</x:t>
   </x:si>
   <x:si>
@@ -184,10 +190,19 @@
     <x:t>Simple</x:t>
   </x:si>
   <x:si>
+    <x:t>Símbolo no encontrado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F7FFFFF</x:t>
+  </x:si>
+  <x:si>
     <x:t>0016</x:t>
   </x:si>
   <x:si>
     <x:t>RSUB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4F0000</x:t>
   </x:si>
   <x:si>
     <x:t>0019</x:t>
@@ -778,7 +793,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:9">
@@ -786,28 +801,28 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:9">
@@ -815,16 +830,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>13</x:v>
@@ -844,28 +859,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:9">
@@ -873,28 +888,28 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:9">
@@ -902,28 +917,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:9">
@@ -931,13 +946,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>15</x:v>
@@ -952,7 +967,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:9">
@@ -960,16 +975,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
         <x:v>13</x:v>
@@ -989,25 +1004,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="I14" s="0" t="s">
         <x:v>15</x:v>
@@ -1018,16 +1033,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
         <x:v>13</x:v>
@@ -1047,16 +1062,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
         <x:v>13</x:v>
@@ -1068,7 +1083,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:9">
@@ -1076,16 +1091,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
         <x:v>13</x:v>
@@ -1097,7 +1112,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:9">
@@ -1105,13 +1120,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
         <x:v>15</x:v>
